--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/TENNESSEE_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/TENNESSEE_2023.xlsx
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C181">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C283">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C292">
